--- a/4_Quarto/categories/SMDimbalance.xlsx
+++ b/4_Quarto/categories/SMDimbalance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowelin\Documents\GitHub\OPTIMA_incidence_survival\4_Quarto\categories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6156B68F-9815-4CBF-9EEC-09D1DFA0DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77A8A47-5AE4-405E-A932-CBEEFD16B62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{10A7F052-5A74-46C2-A64E-2AD5ADE47CFD}"/>
+    <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="15720" xr2:uid="{10A7F052-5A74-46C2-A64E-2AD5ADE47CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="SIGNS_SYMP_Presentation_-1to-12" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SIGNS_SYMP_Presentation_-1to-12'!$A$1:$D$174</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1475,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
